--- a/4.3.1 дифракция света/измерения.xlsx
+++ b/4.3.1 дифракция света/измерения.xlsx
@@ -26,32 +26,17 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="15">
   <si>
     <t>шкала</t>
   </si>
   <si>
-    <t>показания винта, мм</t>
-  </si>
-  <si>
     <t>ширина на фото микроскопа, пикселей</t>
   </si>
   <si>
     <t>погрешность</t>
   </si>
   <si>
-    <t>это фигня</t>
-  </si>
-  <si>
-    <t>кол-во темных полос</t>
-  </si>
-  <si>
-    <t>винт</t>
-  </si>
-  <si>
-    <t>линейка</t>
-  </si>
-  <si>
     <t>фокус линзы</t>
   </si>
   <si>
@@ -65,6 +50,27 @@
   </si>
   <si>
     <t>1 мм</t>
+  </si>
+  <si>
+    <t>винт, мм</t>
+  </si>
+  <si>
+    <t>линейка, см</t>
+  </si>
+  <si>
+    <t>n</t>
+  </si>
+  <si>
+    <t>x_min, mm</t>
+  </si>
+  <si>
+    <t>x_max, mm</t>
+  </si>
+  <si>
+    <t>x_min abs</t>
+  </si>
+  <si>
+    <t>x_max abs</t>
   </si>
 </sst>
 </file>
@@ -101,9 +107,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -386,6 +391,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="16.36328125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
@@ -394,10 +402,10 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -407,39 +415,51 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="19.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="1.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="11.08984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.08984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.453125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="15" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E1" t="s">
-        <v>6</v>
+        <v>8</v>
+      </c>
+      <c r="F1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1" t="s">
+        <v>14</v>
       </c>
       <c r="H1" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="I1" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>0</v>
       </c>
@@ -455,17 +475,27 @@
       <c r="E2">
         <v>10.89</v>
       </c>
+      <c r="F2">
+        <f>B2*10 +D2</f>
+        <v>559.89</v>
+      </c>
+      <c r="G2">
+        <f>C2*10 +E2</f>
+        <v>559.89</v>
+      </c>
       <c r="H2">
+        <f>F2-$F$2</f>
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <f>G2-$F$2</f>
+        <v>0</v>
+      </c>
+      <c r="L2">
         <v>210</v>
       </c>
-      <c r="I2" s="1">
-        <v>1.65</v>
-      </c>
-      <c r="J2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>1</v>
       </c>
@@ -481,14 +511,27 @@
       <c r="E3">
         <v>10.89</v>
       </c>
-      <c r="H3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="F3">
+        <f t="shared" ref="F3:F9" si="0">B3*10 +D3</f>
+        <v>609.89</v>
+      </c>
+      <c r="G3">
+        <f t="shared" ref="G3:G9" si="1">C3*10 +E3</f>
+        <v>624.89</v>
+      </c>
+      <c r="H3">
+        <f t="shared" ref="H3:H9" si="2">F3-$F$2</f>
+        <v>50</v>
+      </c>
+      <c r="I3">
+        <f t="shared" ref="I3:I9" si="3">G3-$F$2</f>
+        <v>65</v>
+      </c>
+      <c r="L3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>2</v>
       </c>
@@ -504,14 +547,27 @@
       <c r="E4">
         <v>10.89</v>
       </c>
+      <c r="F4">
+        <f t="shared" si="0"/>
+        <v>589.89</v>
+      </c>
+      <c r="G4">
+        <f t="shared" si="1"/>
+        <v>600.89</v>
+      </c>
       <c r="H4">
+        <f t="shared" si="2"/>
+        <v>30</v>
+      </c>
+      <c r="I4">
+        <f t="shared" si="3"/>
+        <v>41</v>
+      </c>
+      <c r="L4">
         <v>1</v>
       </c>
-      <c r="I4">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>3</v>
       </c>
@@ -519,7 +575,7 @@
         <v>57.2</v>
       </c>
       <c r="C5">
-        <v>67.7</v>
+        <v>57.7</v>
       </c>
       <c r="D5">
         <v>10.89</v>
@@ -527,8 +583,24 @@
       <c r="E5">
         <v>10.89</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="F5">
+        <f t="shared" si="0"/>
+        <v>582.89</v>
+      </c>
+      <c r="G5">
+        <f t="shared" si="1"/>
+        <v>587.89</v>
+      </c>
+      <c r="H5">
+        <f t="shared" si="2"/>
+        <v>23</v>
+      </c>
+      <c r="I5">
+        <f t="shared" si="3"/>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>4</v>
       </c>
@@ -544,8 +616,24 @@
       <c r="E6">
         <v>10.89</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="F6">
+        <f t="shared" si="0"/>
+        <v>579.89</v>
+      </c>
+      <c r="G6">
+        <f t="shared" si="1"/>
+        <v>582.89</v>
+      </c>
+      <c r="H6">
+        <f t="shared" si="2"/>
+        <v>20</v>
+      </c>
+      <c r="I6">
+        <f t="shared" si="3"/>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>5</v>
       </c>
@@ -561,8 +649,24 @@
       <c r="E7">
         <v>10.89</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="F7">
+        <f t="shared" si="0"/>
+        <v>575.89</v>
+      </c>
+      <c r="G7">
+        <f t="shared" si="1"/>
+        <v>575.89</v>
+      </c>
+      <c r="H7">
+        <f t="shared" si="2"/>
+        <v>16</v>
+      </c>
+      <c r="I7">
+        <f t="shared" si="3"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>6</v>
       </c>
@@ -573,13 +677,29 @@
         <v>56.5</v>
       </c>
       <c r="D8">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="E8">
         <v>10.1</v>
       </c>
-      <c r="E8">
-        <v>8.1999999999999993</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="F8">
+        <f t="shared" si="0"/>
+        <v>573.20000000000005</v>
+      </c>
+      <c r="G8">
+        <f t="shared" si="1"/>
+        <v>575.1</v>
+      </c>
+      <c r="H8">
+        <f t="shared" si="2"/>
+        <v>13.310000000000059</v>
+      </c>
+      <c r="I8">
+        <f t="shared" si="3"/>
+        <v>15.210000000000036</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>7</v>
       </c>
@@ -590,10 +710,26 @@
         <v>56.5</v>
       </c>
       <c r="D9">
+        <v>6.34</v>
+      </c>
+      <c r="E9">
         <v>7.18</v>
       </c>
-      <c r="E9">
-        <v>6.34</v>
+      <c r="F9">
+        <f t="shared" si="0"/>
+        <v>571.34</v>
+      </c>
+      <c r="G9">
+        <f t="shared" si="1"/>
+        <v>572.17999999999995</v>
+      </c>
+      <c r="H9">
+        <f t="shared" si="2"/>
+        <v>11.450000000000045</v>
+      </c>
+      <c r="I9">
+        <f t="shared" si="3"/>
+        <v>12.289999999999964</v>
       </c>
     </row>
   </sheetData>
@@ -609,15 +745,15 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D1" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D2">
         <v>343</v>
